--- a/dev/epa_monitoring_data_K_2023-05-27_to_2024-05-26.xlsx
+++ b/dev/epa_monitoring_data_K_2023-05-27_to_2024-05-26.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H617"/>
+  <dimension ref="A1:H645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
@@ -455,6 +455,9 @@
           <t>per cent by volume</t>
         </is>
       </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
       <c r="E2">
         <v>978</v>
       </c>
@@ -1528,6 +1531,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
       <c r="E39">
         <v>4</v>
       </c>
@@ -1818,6 +1824,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
       <c r="E49">
         <v>4</v>
       </c>
@@ -2137,6 +2146,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
       <c r="E60">
         <v>4</v>
       </c>
@@ -2166,6 +2178,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
       <c r="E61">
         <v>1</v>
       </c>
@@ -2282,6 +2297,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
       <c r="E65">
         <v>1</v>
       </c>
@@ -2311,6 +2329,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
       <c r="E66">
         <v>4</v>
       </c>
@@ -2804,6 +2825,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
       <c r="E83">
         <v>11</v>
       </c>
@@ -3094,6 +3118,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
       <c r="E93">
         <v>11</v>
       </c>
@@ -3413,6 +3440,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
       <c r="E104">
         <v>11</v>
       </c>
@@ -3471,6 +3501,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D106">
+        <v>4</v>
+      </c>
       <c r="E106">
         <v>8</v>
       </c>
@@ -3587,6 +3620,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D110">
+        <v>4</v>
+      </c>
       <c r="E110">
         <v>8</v>
       </c>
@@ -3616,6 +3652,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D111">
+        <v>4</v>
+      </c>
       <c r="E111">
         <v>11</v>
       </c>
@@ -4109,6 +4148,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D128">
+        <v>4</v>
+      </c>
       <c r="E128">
         <v>4</v>
       </c>
@@ -4399,6 +4441,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D138">
+        <v>4</v>
+      </c>
       <c r="E138">
         <v>4</v>
       </c>
@@ -4718,6 +4763,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D149">
+        <v>4</v>
+      </c>
       <c r="E149">
         <v>4</v>
       </c>
@@ -4776,6 +4824,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D151">
+        <v>4</v>
+      </c>
       <c r="E151">
         <v>4</v>
       </c>
@@ -4892,6 +4943,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D155">
+        <v>4</v>
+      </c>
       <c r="E155">
         <v>4</v>
       </c>
@@ -4921,6 +4975,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D156">
+        <v>4</v>
+      </c>
       <c r="E156">
         <v>4</v>
       </c>
@@ -5414,6 +5471,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D173">
+        <v>4</v>
+      </c>
       <c r="E173">
         <v>5</v>
       </c>
@@ -5704,6 +5764,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D183">
+        <v>4</v>
+      </c>
       <c r="E183">
         <v>5</v>
       </c>
@@ -6023,6 +6086,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D194">
+        <v>4</v>
+      </c>
       <c r="E194">
         <v>5</v>
       </c>
@@ -6081,6 +6147,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D196">
+        <v>4</v>
+      </c>
       <c r="E196">
         <v>5</v>
       </c>
@@ -6197,6 +6266,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D200">
+        <v>4</v>
+      </c>
       <c r="E200">
         <v>5</v>
       </c>
@@ -6226,6 +6298,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D201">
+        <v>4</v>
+      </c>
       <c r="E201">
         <v>5</v>
       </c>
@@ -6719,6 +6794,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D218">
+        <v>4</v>
+      </c>
       <c r="E218">
         <v>10</v>
       </c>
@@ -6980,6 +7058,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D227">
+        <v>4</v>
+      </c>
       <c r="E227">
         <v>10</v>
       </c>
@@ -7270,6 +7351,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D237">
+        <v>4</v>
+      </c>
       <c r="E237">
         <v>10</v>
       </c>
@@ -7328,6 +7412,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D239">
+        <v>4</v>
+      </c>
       <c r="E239">
         <v>8</v>
       </c>
@@ -7415,6 +7502,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D242">
+        <v>4</v>
+      </c>
       <c r="E242">
         <v>8</v>
       </c>
@@ -7444,6 +7534,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D243">
+        <v>4</v>
+      </c>
       <c r="E243">
         <v>10</v>
       </c>
@@ -7560,6 +7653,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D247">
+        <v>4</v>
+      </c>
       <c r="E247">
         <v>4</v>
       </c>
@@ -7821,6 +7917,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D256">
+        <v>4</v>
+      </c>
       <c r="E256">
         <v>4</v>
       </c>
@@ -8111,6 +8210,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D266">
+        <v>4</v>
+      </c>
       <c r="E266">
         <v>4</v>
       </c>
@@ -8140,6 +8242,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D267">
+        <v>4</v>
+      </c>
       <c r="E267">
         <v>1</v>
       </c>
@@ -8227,6 +8332,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D270">
+        <v>4</v>
+      </c>
       <c r="E270">
         <v>1</v>
       </c>
@@ -8256,6 +8364,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D271">
+        <v>4</v>
+      </c>
       <c r="E271">
         <v>4</v>
       </c>
@@ -8517,6 +8628,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D280">
+        <v>4</v>
+      </c>
       <c r="E280">
         <v>11</v>
       </c>
@@ -8865,6 +8979,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D292">
+        <v>4</v>
+      </c>
       <c r="E292">
         <v>12</v>
       </c>
@@ -9677,6 +9794,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D320">
+        <v>4</v>
+      </c>
       <c r="E320">
         <v>12</v>
       </c>
@@ -9764,6 +9884,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D323">
+        <v>4</v>
+      </c>
       <c r="E323">
         <v>8</v>
       </c>
@@ -9880,6 +10003,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D327">
+        <v>4</v>
+      </c>
       <c r="E327">
         <v>8</v>
       </c>
@@ -9909,6 +10035,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D328">
+        <v>4</v>
+      </c>
       <c r="E328">
         <v>11</v>
       </c>
@@ -10373,6 +10502,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D344">
+        <v>4</v>
+      </c>
       <c r="E344">
         <v>4</v>
       </c>
@@ -10402,6 +10534,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D345">
+        <v>4</v>
+      </c>
       <c r="E345">
         <v>4</v>
       </c>
@@ -10431,6 +10566,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D346">
+        <v>1</v>
+      </c>
       <c r="E346">
         <v>1</v>
       </c>
@@ -10460,6 +10598,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D347">
+        <v>1</v>
+      </c>
       <c r="E347">
         <v>1</v>
       </c>
@@ -10489,6 +10630,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D348">
+        <v>1</v>
+      </c>
       <c r="E348">
         <v>1</v>
       </c>
@@ -10518,6 +10662,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D349">
+        <v>1</v>
+      </c>
       <c r="E349">
         <v>1</v>
       </c>
@@ -10547,6 +10694,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D350">
+        <v>4</v>
+      </c>
       <c r="E350">
         <v>4</v>
       </c>
@@ -10576,6 +10726,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D351">
+        <v>4</v>
+      </c>
       <c r="E351">
         <v>4</v>
       </c>
@@ -10605,6 +10758,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D352">
+        <v>1</v>
+      </c>
       <c r="E352">
         <v>1</v>
       </c>
@@ -10634,6 +10790,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D353">
+        <v>1</v>
+      </c>
       <c r="E353">
         <v>1</v>
       </c>
@@ -10663,6 +10822,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D354">
+        <v>4</v>
+      </c>
       <c r="E354">
         <v>4</v>
       </c>
@@ -10692,6 +10854,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D355">
+        <v>1</v>
+      </c>
       <c r="E355">
         <v>1</v>
       </c>
@@ -10721,6 +10886,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D356">
+        <v>1</v>
+      </c>
       <c r="E356">
         <v>1</v>
       </c>
@@ -10750,6 +10918,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D357">
+        <v>4</v>
+      </c>
       <c r="E357">
         <v>1</v>
       </c>
@@ -10779,6 +10950,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D358">
+        <v>1</v>
+      </c>
       <c r="E358">
         <v>1</v>
       </c>
@@ -10808,6 +10982,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D359">
+        <v>4</v>
+      </c>
       <c r="E359">
         <v>4</v>
       </c>
@@ -10837,6 +11014,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D360">
+        <v>1</v>
+      </c>
       <c r="E360">
         <v>1</v>
       </c>
@@ -10866,6 +11046,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D361">
+        <v>1</v>
+      </c>
       <c r="E361">
         <v>1</v>
       </c>
@@ -10895,6 +11078,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D362">
+        <v>1</v>
+      </c>
       <c r="E362">
         <v>1</v>
       </c>
@@ -10924,6 +11110,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D363">
+        <v>4</v>
+      </c>
       <c r="E363">
         <v>1</v>
       </c>
@@ -10953,6 +11142,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D364">
+        <v>4</v>
+      </c>
       <c r="E364">
         <v>1</v>
       </c>
@@ -10982,6 +11174,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D365">
+        <v>4</v>
+      </c>
       <c r="E365">
         <v>4</v>
       </c>
@@ -11011,6 +11206,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D366">
+        <v>4</v>
+      </c>
       <c r="E366">
         <v>4</v>
       </c>
@@ -11040,6 +11238,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D367">
+        <v>4</v>
+      </c>
       <c r="E367">
         <v>4</v>
       </c>
@@ -11069,6 +11270,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D368">
+        <v>4</v>
+      </c>
       <c r="E368">
         <v>2</v>
       </c>
@@ -11098,6 +11302,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D369">
+        <v>4</v>
+      </c>
       <c r="E369">
         <v>4</v>
       </c>
@@ -11127,6 +11334,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D370">
+        <v>1</v>
+      </c>
       <c r="E370">
         <v>1</v>
       </c>
@@ -11156,6 +11366,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D371">
+        <v>4</v>
+      </c>
       <c r="E371">
         <v>4</v>
       </c>
@@ -11185,6 +11398,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D372">
+        <v>4</v>
+      </c>
       <c r="E372">
         <v>4</v>
       </c>
@@ -11214,6 +11430,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D373">
+        <v>1</v>
+      </c>
       <c r="E373">
         <v>1</v>
       </c>
@@ -11243,6 +11462,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D374">
+        <v>1</v>
+      </c>
       <c r="E374">
         <v>1</v>
       </c>
@@ -11272,6 +11494,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D375">
+        <v>1</v>
+      </c>
       <c r="E375">
         <v>1</v>
       </c>
@@ -11301,6 +11526,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D376">
+        <v>1</v>
+      </c>
       <c r="E376">
         <v>1</v>
       </c>
@@ -11330,6 +11558,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D377">
+        <v>1</v>
+      </c>
       <c r="E377">
         <v>1</v>
       </c>
@@ -11359,6 +11590,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D378">
+        <v>1</v>
+      </c>
       <c r="E378">
         <v>1</v>
       </c>
@@ -11388,6 +11622,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D379">
+        <v>1</v>
+      </c>
       <c r="E379">
         <v>1</v>
       </c>
@@ -11417,6 +11654,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D380">
+        <v>1</v>
+      </c>
       <c r="E380">
         <v>1</v>
       </c>
@@ -11446,6 +11686,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D381">
+        <v>1</v>
+      </c>
       <c r="E381">
         <v>1</v>
       </c>
@@ -11475,6 +11718,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D382">
+        <v>1</v>
+      </c>
       <c r="E382">
         <v>1</v>
       </c>
@@ -11504,6 +11750,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D383">
+        <v>1</v>
+      </c>
       <c r="E383">
         <v>1</v>
       </c>
@@ -11533,6 +11782,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D384">
+        <v>1</v>
+      </c>
       <c r="E384">
         <v>1</v>
       </c>
@@ -11562,6 +11814,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D385">
+        <v>1</v>
+      </c>
       <c r="E385">
         <v>1</v>
       </c>
@@ -11591,6 +11846,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
       <c r="E386">
         <v>1</v>
       </c>
@@ -11620,6 +11878,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D387">
+        <v>1</v>
+      </c>
       <c r="E387">
         <v>1</v>
       </c>
@@ -11649,6 +11910,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D388">
+        <v>1</v>
+      </c>
       <c r="E388">
         <v>1</v>
       </c>
@@ -11678,6 +11942,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D389">
+        <v>1</v>
+      </c>
       <c r="E389">
         <v>1</v>
       </c>
@@ -11707,6 +11974,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D390">
+        <v>1</v>
+      </c>
       <c r="E390">
         <v>1</v>
       </c>
@@ -11736,6 +12006,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D391">
+        <v>4</v>
+      </c>
       <c r="E391">
         <v>4</v>
       </c>
@@ -11765,6 +12038,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D392">
+        <v>1</v>
+      </c>
       <c r="E392">
         <v>1</v>
       </c>
@@ -11794,6 +12070,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D393">
+        <v>1</v>
+      </c>
       <c r="E393">
         <v>1</v>
       </c>
@@ -11823,6 +12102,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D394">
+        <v>4</v>
+      </c>
       <c r="E394">
         <v>4</v>
       </c>
@@ -11852,6 +12134,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D395">
+        <v>1</v>
+      </c>
       <c r="E395">
         <v>1</v>
       </c>
@@ -11881,6 +12166,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D396">
+        <v>1</v>
+      </c>
       <c r="E396">
         <v>1</v>
       </c>
@@ -11910,6 +12198,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D397">
+        <v>1</v>
+      </c>
       <c r="E397">
         <v>1</v>
       </c>
@@ -11939,6 +12230,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D398">
+        <v>1</v>
+      </c>
       <c r="E398">
         <v>1</v>
       </c>
@@ -11968,6 +12262,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D399">
+        <v>1</v>
+      </c>
       <c r="E399">
         <v>1</v>
       </c>
@@ -11997,6 +12294,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D400">
+        <v>4</v>
+      </c>
       <c r="E400">
         <v>4</v>
       </c>
@@ -12026,6 +12326,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D401">
+        <v>4</v>
+      </c>
       <c r="E401">
         <v>4</v>
       </c>
@@ -12055,6 +12358,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D402">
+        <v>1</v>
+      </c>
       <c r="E402">
         <v>1</v>
       </c>
@@ -12084,6 +12390,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D403">
+        <v>1</v>
+      </c>
       <c r="E403">
         <v>1</v>
       </c>
@@ -12113,6 +12422,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D404">
+        <v>1</v>
+      </c>
       <c r="E404">
         <v>1</v>
       </c>
@@ -12142,6 +12454,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D405">
+        <v>1</v>
+      </c>
       <c r="E405">
         <v>1</v>
       </c>
@@ -12171,6 +12486,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D406">
+        <v>4</v>
+      </c>
       <c r="E406">
         <v>4</v>
       </c>
@@ -12200,6 +12518,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D407">
+        <v>1</v>
+      </c>
       <c r="E407">
         <v>1</v>
       </c>
@@ -12229,6 +12550,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D408">
+        <v>1</v>
+      </c>
       <c r="E408">
         <v>1</v>
       </c>
@@ -12258,6 +12582,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D409">
+        <v>1</v>
+      </c>
       <c r="E409">
         <v>1</v>
       </c>
@@ -12287,6 +12614,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D410">
+        <v>1</v>
+      </c>
       <c r="E410">
         <v>1</v>
       </c>
@@ -12316,6 +12646,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D411">
+        <v>1</v>
+      </c>
       <c r="E411">
         <v>1</v>
       </c>
@@ -12345,6 +12678,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D412">
+        <v>1</v>
+      </c>
       <c r="E412">
         <v>1</v>
       </c>
@@ -12374,6 +12710,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D413">
+        <v>1</v>
+      </c>
       <c r="E413">
         <v>1</v>
       </c>
@@ -12403,6 +12742,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D414">
+        <v>1</v>
+      </c>
       <c r="E414">
         <v>1</v>
       </c>
@@ -12432,6 +12774,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D415">
+        <v>1</v>
+      </c>
       <c r="E415">
         <v>1</v>
       </c>
@@ -12461,6 +12806,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D416">
+        <v>1</v>
+      </c>
       <c r="E416">
         <v>1</v>
       </c>
@@ -12490,6 +12838,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D417">
+        <v>4</v>
+      </c>
       <c r="E417">
         <v>1</v>
       </c>
@@ -12519,6 +12870,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D418">
+        <v>1</v>
+      </c>
       <c r="E418">
         <v>1</v>
       </c>
@@ -12548,6 +12902,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D419">
+        <v>1</v>
+      </c>
       <c r="E419">
         <v>1</v>
       </c>
@@ -12577,6 +12934,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D420">
+        <v>1</v>
+      </c>
       <c r="E420">
         <v>1</v>
       </c>
@@ -12606,6 +12966,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D421">
+        <v>1</v>
+      </c>
       <c r="E421">
         <v>1</v>
       </c>
@@ -12635,6 +12998,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D422">
+        <v>4</v>
+      </c>
       <c r="E422">
         <v>4</v>
       </c>
@@ -12664,6 +13030,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D423">
+        <v>1</v>
+      </c>
       <c r="E423">
         <v>1</v>
       </c>
@@ -12693,6 +13062,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D424">
+        <v>1</v>
+      </c>
       <c r="E424">
         <v>1</v>
       </c>
@@ -12722,6 +13094,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D425">
+        <v>1</v>
+      </c>
       <c r="E425">
         <v>1</v>
       </c>
@@ -12751,6 +13126,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D426">
+        <v>1</v>
+      </c>
       <c r="E426">
         <v>1</v>
       </c>
@@ -12780,6 +13158,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D427">
+        <v>1</v>
+      </c>
       <c r="E427">
         <v>1</v>
       </c>
@@ -12809,6 +13190,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D428">
+        <v>1</v>
+      </c>
       <c r="E428">
         <v>1</v>
       </c>
@@ -12838,6 +13222,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D429">
+        <v>1</v>
+      </c>
       <c r="E429">
         <v>1</v>
       </c>
@@ -12867,6 +13254,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D430">
+        <v>1</v>
+      </c>
       <c r="E430">
         <v>1</v>
       </c>
@@ -12896,6 +13286,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D431">
+        <v>4</v>
+      </c>
       <c r="E431">
         <v>1</v>
       </c>
@@ -12925,6 +13318,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D432">
+        <v>4</v>
+      </c>
       <c r="E432">
         <v>1</v>
       </c>
@@ -12954,6 +13350,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D433">
+        <v>1</v>
+      </c>
       <c r="E433">
         <v>1</v>
       </c>
@@ -12983,6 +13382,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D434">
+        <v>4</v>
+      </c>
       <c r="E434">
         <v>4</v>
       </c>
@@ -13012,6 +13414,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D435">
+        <v>1</v>
+      </c>
       <c r="E435">
         <v>1</v>
       </c>
@@ -13041,6 +13446,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D436">
+        <v>4</v>
+      </c>
       <c r="E436">
         <v>4</v>
       </c>
@@ -13070,6 +13478,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D437">
+        <v>4</v>
+      </c>
       <c r="E437">
         <v>4</v>
       </c>
@@ -13099,6 +13510,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D438">
+        <v>4</v>
+      </c>
       <c r="E438">
         <v>2</v>
       </c>
@@ -13128,6 +13542,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D439">
+        <v>4</v>
+      </c>
       <c r="E439">
         <v>4</v>
       </c>
@@ -13157,6 +13574,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D440">
+        <v>1</v>
+      </c>
       <c r="E440">
         <v>1</v>
       </c>
@@ -13186,6 +13606,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D441">
+        <v>4</v>
+      </c>
       <c r="E441">
         <v>4</v>
       </c>
@@ -13215,6 +13638,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D442">
+        <v>4</v>
+      </c>
       <c r="E442">
         <v>4</v>
       </c>
@@ -13244,6 +13670,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D443">
+        <v>1</v>
+      </c>
       <c r="E443">
         <v>1</v>
       </c>
@@ -13273,6 +13702,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D444">
+        <v>1</v>
+      </c>
       <c r="E444">
         <v>1</v>
       </c>
@@ -13302,6 +13734,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D445">
+        <v>1</v>
+      </c>
       <c r="E445">
         <v>1</v>
       </c>
@@ -13331,6 +13766,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D446">
+        <v>1</v>
+      </c>
       <c r="E446">
         <v>1</v>
       </c>
@@ -13360,6 +13798,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D447">
+        <v>1</v>
+      </c>
       <c r="E447">
         <v>1</v>
       </c>
@@ -13389,6 +13830,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D448">
+        <v>1</v>
+      </c>
       <c r="E448">
         <v>1</v>
       </c>
@@ -13418,6 +13862,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D449">
+        <v>1</v>
+      </c>
       <c r="E449">
         <v>1</v>
       </c>
@@ -13447,6 +13894,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D450">
+        <v>1</v>
+      </c>
       <c r="E450">
         <v>1</v>
       </c>
@@ -13476,6 +13926,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D451">
+        <v>1</v>
+      </c>
       <c r="E451">
         <v>1</v>
       </c>
@@ -13505,6 +13958,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D452">
+        <v>1</v>
+      </c>
       <c r="E452">
         <v>1</v>
       </c>
@@ -13534,6 +13990,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D453">
+        <v>1</v>
+      </c>
       <c r="E453">
         <v>1</v>
       </c>
@@ -13563,6 +14022,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D454">
+        <v>1</v>
+      </c>
       <c r="E454">
         <v>1</v>
       </c>
@@ -13621,6 +14083,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D456">
+        <v>1</v>
+      </c>
       <c r="E456">
         <v>1</v>
       </c>
@@ -13650,6 +14115,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D457">
+        <v>1</v>
+      </c>
       <c r="E457">
         <v>1</v>
       </c>
@@ -13679,6 +14147,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D458">
+        <v>1</v>
+      </c>
       <c r="E458">
         <v>1</v>
       </c>
@@ -13708,6 +14179,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D459">
+        <v>1</v>
+      </c>
       <c r="E459">
         <v>1</v>
       </c>
@@ -13737,6 +14211,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D460">
+        <v>1</v>
+      </c>
       <c r="E460">
         <v>1</v>
       </c>
@@ -13766,6 +14243,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D461">
+        <v>1</v>
+      </c>
       <c r="E461">
         <v>1</v>
       </c>
@@ -13795,6 +14275,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D462">
+        <v>4</v>
+      </c>
       <c r="E462">
         <v>4</v>
       </c>
@@ -13824,6 +14307,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D463">
+        <v>1</v>
+      </c>
       <c r="E463">
         <v>1</v>
       </c>
@@ -13853,6 +14339,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D464">
+        <v>1</v>
+      </c>
       <c r="E464">
         <v>1</v>
       </c>
@@ -13882,6 +14371,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D465">
+        <v>4</v>
+      </c>
       <c r="E465">
         <v>4</v>
       </c>
@@ -13911,6 +14403,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D466">
+        <v>1</v>
+      </c>
       <c r="E466">
         <v>1</v>
       </c>
@@ -13940,6 +14435,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D467">
+        <v>1</v>
+      </c>
       <c r="E467">
         <v>1</v>
       </c>
@@ -13969,6 +14467,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D468">
+        <v>1</v>
+      </c>
       <c r="E468">
         <v>1</v>
       </c>
@@ -13998,6 +14499,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D469">
+        <v>1</v>
+      </c>
       <c r="E469">
         <v>1</v>
       </c>
@@ -14056,6 +14560,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D471">
+        <v>1</v>
+      </c>
       <c r="E471">
         <v>1</v>
       </c>
@@ -14085,6 +14592,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D472">
+        <v>4</v>
+      </c>
       <c r="E472">
         <v>4</v>
       </c>
@@ -14114,6 +14624,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D473">
+        <v>4</v>
+      </c>
       <c r="E473">
         <v>4</v>
       </c>
@@ -14143,6 +14656,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D474">
+        <v>1</v>
+      </c>
       <c r="E474">
         <v>1</v>
       </c>
@@ -14172,6 +14688,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D475">
+        <v>1</v>
+      </c>
       <c r="E475">
         <v>1</v>
       </c>
@@ -14201,6 +14720,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D476">
+        <v>1</v>
+      </c>
       <c r="E476">
         <v>1</v>
       </c>
@@ -14230,6 +14752,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D477">
+        <v>1</v>
+      </c>
       <c r="E477">
         <v>1</v>
       </c>
@@ -14259,6 +14784,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D478">
+        <v>4</v>
+      </c>
       <c r="E478">
         <v>4</v>
       </c>
@@ -14288,6 +14816,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D479">
+        <v>1</v>
+      </c>
       <c r="E479">
         <v>1</v>
       </c>
@@ -14317,6 +14848,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D480">
+        <v>1</v>
+      </c>
       <c r="E480">
         <v>1</v>
       </c>
@@ -14346,6 +14880,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D481">
+        <v>1</v>
+      </c>
       <c r="E481">
         <v>1</v>
       </c>
@@ -14375,6 +14912,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D482">
+        <v>1</v>
+      </c>
       <c r="E482">
         <v>1</v>
       </c>
@@ -14404,6 +14944,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D483">
+        <v>1</v>
+      </c>
       <c r="E483">
         <v>1</v>
       </c>
@@ -14433,6 +14976,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D484">
+        <v>1</v>
+      </c>
       <c r="E484">
         <v>1</v>
       </c>
@@ -14462,6 +15008,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D485">
+        <v>1</v>
+      </c>
       <c r="E485">
         <v>1</v>
       </c>
@@ -14491,6 +15040,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D486">
+        <v>1</v>
+      </c>
       <c r="E486">
         <v>1</v>
       </c>
@@ -14520,6 +15072,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D487">
+        <v>1</v>
+      </c>
       <c r="E487">
         <v>1</v>
       </c>
@@ -14549,6 +15104,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D488">
+        <v>1</v>
+      </c>
       <c r="E488">
         <v>1</v>
       </c>
@@ -14578,6 +15136,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D489">
+        <v>4</v>
+      </c>
       <c r="E489">
         <v>1</v>
       </c>
@@ -14607,6 +15168,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D490">
+        <v>1</v>
+      </c>
       <c r="E490">
         <v>1</v>
       </c>
@@ -14636,6 +15200,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D491">
+        <v>1</v>
+      </c>
       <c r="E491">
         <v>1</v>
       </c>
@@ -14665,6 +15232,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D492">
+        <v>1</v>
+      </c>
       <c r="E492">
         <v>1</v>
       </c>
@@ -14694,6 +15264,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D493">
+        <v>1</v>
+      </c>
       <c r="E493">
         <v>1</v>
       </c>
@@ -14723,6 +15296,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D494">
+        <v>4</v>
+      </c>
       <c r="E494">
         <v>4</v>
       </c>
@@ -14752,6 +15328,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D495">
+        <v>1</v>
+      </c>
       <c r="E495">
         <v>1</v>
       </c>
@@ -14781,6 +15360,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D496">
+        <v>1</v>
+      </c>
       <c r="E496">
         <v>1</v>
       </c>
@@ -14810,6 +15392,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D497">
+        <v>1</v>
+      </c>
       <c r="E497">
         <v>1</v>
       </c>
@@ -14839,6 +15424,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D498">
+        <v>1</v>
+      </c>
       <c r="E498">
         <v>1</v>
       </c>
@@ -14868,6 +15456,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D499">
+        <v>1</v>
+      </c>
       <c r="E499">
         <v>1</v>
       </c>
@@ -14897,6 +15488,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D500">
+        <v>1</v>
+      </c>
       <c r="E500">
         <v>1</v>
       </c>
@@ -14926,6 +15520,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D501">
+        <v>1</v>
+      </c>
       <c r="E501">
         <v>1</v>
       </c>
@@ -14955,6 +15552,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D502">
+        <v>1</v>
+      </c>
       <c r="E502">
         <v>1</v>
       </c>
@@ -14984,6 +15584,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D503">
+        <v>4</v>
+      </c>
       <c r="E503">
         <v>1</v>
       </c>
@@ -15013,6 +15616,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D504">
+        <v>4</v>
+      </c>
       <c r="E504">
         <v>1</v>
       </c>
@@ -15042,6 +15648,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D505">
+        <v>1</v>
+      </c>
       <c r="E505">
         <v>1</v>
       </c>
@@ -15071,6 +15680,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D506">
+        <v>4</v>
+      </c>
       <c r="E506">
         <v>4</v>
       </c>
@@ -15100,6 +15712,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D507">
+        <v>1</v>
+      </c>
       <c r="E507">
         <v>1</v>
       </c>
@@ -15129,6 +15744,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D508">
+        <v>4</v>
+      </c>
       <c r="E508">
         <v>4</v>
       </c>
@@ -15158,6 +15776,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D509">
+        <v>4</v>
+      </c>
       <c r="E509">
         <v>4</v>
       </c>
@@ -15187,6 +15808,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D510">
+        <v>4</v>
+      </c>
       <c r="E510">
         <v>2</v>
       </c>
@@ -15216,6 +15840,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D511">
+        <v>4</v>
+      </c>
       <c r="E511">
         <v>4</v>
       </c>
@@ -15245,6 +15872,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D512">
+        <v>1</v>
+      </c>
       <c r="E512">
         <v>1</v>
       </c>
@@ -15274,6 +15904,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D513">
+        <v>4</v>
+      </c>
       <c r="E513">
         <v>4</v>
       </c>
@@ -15303,6 +15936,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D514">
+        <v>4</v>
+      </c>
       <c r="E514">
         <v>4</v>
       </c>
@@ -15332,6 +15968,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D515">
+        <v>1</v>
+      </c>
       <c r="E515">
         <v>1</v>
       </c>
@@ -15361,6 +16000,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
       <c r="E516">
         <v>1</v>
       </c>
@@ -15390,6 +16032,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
       <c r="E517">
         <v>1</v>
       </c>
@@ -15419,6 +16064,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D518">
+        <v>1</v>
+      </c>
       <c r="E518">
         <v>1</v>
       </c>
@@ -15448,6 +16096,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D519">
+        <v>1</v>
+      </c>
       <c r="E519">
         <v>1</v>
       </c>
@@ -15477,6 +16128,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D520">
+        <v>1</v>
+      </c>
       <c r="E520">
         <v>1</v>
       </c>
@@ -15506,6 +16160,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D521">
+        <v>1</v>
+      </c>
       <c r="E521">
         <v>1</v>
       </c>
@@ -15535,6 +16192,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
       <c r="E522">
         <v>1</v>
       </c>
@@ -15564,6 +16224,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D523">
+        <v>1</v>
+      </c>
       <c r="E523">
         <v>1</v>
       </c>
@@ -15593,6 +16256,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D524">
+        <v>1</v>
+      </c>
       <c r="E524">
         <v>1</v>
       </c>
@@ -15622,6 +16288,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D525">
+        <v>1</v>
+      </c>
       <c r="E525">
         <v>1</v>
       </c>
@@ -15651,6 +16320,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D526">
+        <v>1</v>
+      </c>
       <c r="E526">
         <v>1</v>
       </c>
@@ -15709,6 +16381,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D528">
+        <v>1</v>
+      </c>
       <c r="E528">
         <v>1</v>
       </c>
@@ -15738,6 +16413,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D529">
+        <v>1</v>
+      </c>
       <c r="E529">
         <v>1</v>
       </c>
@@ -15767,6 +16445,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D530">
+        <v>1</v>
+      </c>
       <c r="E530">
         <v>1</v>
       </c>
@@ -15796,6 +16477,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D531">
+        <v>1</v>
+      </c>
       <c r="E531">
         <v>1</v>
       </c>
@@ -15825,6 +16509,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D532">
+        <v>1</v>
+      </c>
       <c r="E532">
         <v>1</v>
       </c>
@@ -15854,6 +16541,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D533">
+        <v>1</v>
+      </c>
       <c r="E533">
         <v>1</v>
       </c>
@@ -15883,6 +16573,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D534">
+        <v>4</v>
+      </c>
       <c r="E534">
         <v>4</v>
       </c>
@@ -15912,6 +16605,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D535">
+        <v>1</v>
+      </c>
       <c r="E535">
         <v>1</v>
       </c>
@@ -15941,6 +16637,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D536">
+        <v>1</v>
+      </c>
       <c r="E536">
         <v>1</v>
       </c>
@@ -15970,6 +16669,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D537">
+        <v>4</v>
+      </c>
       <c r="E537">
         <v>4</v>
       </c>
@@ -15999,6 +16701,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D538">
+        <v>1</v>
+      </c>
       <c r="E538">
         <v>1</v>
       </c>
@@ -16028,6 +16733,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D539">
+        <v>1</v>
+      </c>
       <c r="E539">
         <v>1</v>
       </c>
@@ -16057,6 +16765,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D540">
+        <v>1</v>
+      </c>
       <c r="E540">
         <v>1</v>
       </c>
@@ -16086,6 +16797,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D541">
+        <v>1</v>
+      </c>
       <c r="E541">
         <v>1</v>
       </c>
@@ -16144,6 +16858,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D543">
+        <v>1</v>
+      </c>
       <c r="E543">
         <v>1</v>
       </c>
@@ -16173,6 +16890,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D544">
+        <v>4</v>
+      </c>
       <c r="E544">
         <v>4</v>
       </c>
@@ -16202,6 +16922,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D545">
+        <v>4</v>
+      </c>
       <c r="E545">
         <v>4</v>
       </c>
@@ -16231,6 +16954,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D546">
+        <v>1</v>
+      </c>
       <c r="E546">
         <v>1</v>
       </c>
@@ -16260,6 +16986,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D547">
+        <v>1</v>
+      </c>
       <c r="E547">
         <v>1</v>
       </c>
@@ -16289,6 +17018,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D548">
+        <v>1</v>
+      </c>
       <c r="E548">
         <v>1</v>
       </c>
@@ -16318,6 +17050,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D549">
+        <v>1</v>
+      </c>
       <c r="E549">
         <v>1</v>
       </c>
@@ -16347,6 +17082,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D550">
+        <v>4</v>
+      </c>
       <c r="E550">
         <v>4</v>
       </c>
@@ -16376,6 +17114,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D551">
+        <v>1</v>
+      </c>
       <c r="E551">
         <v>1</v>
       </c>
@@ -16405,6 +17146,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D552">
+        <v>1</v>
+      </c>
       <c r="E552">
         <v>1</v>
       </c>
@@ -16434,6 +17178,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D553">
+        <v>1</v>
+      </c>
       <c r="E553">
         <v>1</v>
       </c>
@@ -16463,6 +17210,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D554">
+        <v>1</v>
+      </c>
       <c r="E554">
         <v>1</v>
       </c>
@@ -16492,6 +17242,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D555">
+        <v>1</v>
+      </c>
       <c r="E555">
         <v>1</v>
       </c>
@@ -16521,6 +17274,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D556">
+        <v>1</v>
+      </c>
       <c r="E556">
         <v>1</v>
       </c>
@@ -16550,6 +17306,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D557">
+        <v>1</v>
+      </c>
       <c r="E557">
         <v>1</v>
       </c>
@@ -16579,6 +17338,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D558">
+        <v>1</v>
+      </c>
       <c r="E558">
         <v>1</v>
       </c>
@@ -16608,6 +17370,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D559">
+        <v>1</v>
+      </c>
       <c r="E559">
         <v>1</v>
       </c>
@@ -16637,6 +17402,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D560">
+        <v>1</v>
+      </c>
       <c r="E560">
         <v>1</v>
       </c>
@@ -16666,6 +17434,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D561">
+        <v>4</v>
+      </c>
       <c r="E561">
         <v>1</v>
       </c>
@@ -16695,6 +17466,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D562">
+        <v>1</v>
+      </c>
       <c r="E562">
         <v>1</v>
       </c>
@@ -16724,6 +17498,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D563">
+        <v>1</v>
+      </c>
       <c r="E563">
         <v>1</v>
       </c>
@@ -16753,6 +17530,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
       <c r="E564">
         <v>1</v>
       </c>
@@ -16782,6 +17562,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D565">
+        <v>1</v>
+      </c>
       <c r="E565">
         <v>1</v>
       </c>
@@ -16811,6 +17594,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D566">
+        <v>4</v>
+      </c>
       <c r="E566">
         <v>4</v>
       </c>
@@ -16840,6 +17626,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D567">
+        <v>1</v>
+      </c>
       <c r="E567">
         <v>1</v>
       </c>
@@ -16869,6 +17658,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D568">
+        <v>1</v>
+      </c>
       <c r="E568">
         <v>1</v>
       </c>
@@ -16898,6 +17690,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D569">
+        <v>1</v>
+      </c>
       <c r="E569">
         <v>1</v>
       </c>
@@ -16927,6 +17722,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D570">
+        <v>1</v>
+      </c>
       <c r="E570">
         <v>1</v>
       </c>
@@ -16956,6 +17754,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D571">
+        <v>1</v>
+      </c>
       <c r="E571">
         <v>1</v>
       </c>
@@ -16985,6 +17786,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D572">
+        <v>1</v>
+      </c>
       <c r="E572">
         <v>1</v>
       </c>
@@ -17014,6 +17818,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D573">
+        <v>1</v>
+      </c>
       <c r="E573">
         <v>1</v>
       </c>
@@ -17043,6 +17850,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D574">
+        <v>1</v>
+      </c>
       <c r="E574">
         <v>1</v>
       </c>
@@ -17072,6 +17882,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D575">
+        <v>4</v>
+      </c>
       <c r="E575">
         <v>1</v>
       </c>
@@ -17101,6 +17914,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D576">
+        <v>4</v>
+      </c>
       <c r="E576">
         <v>1</v>
       </c>
@@ -17130,6 +17946,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D577">
+        <v>1</v>
+      </c>
       <c r="E577">
         <v>1</v>
       </c>
@@ -17159,6 +17978,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D578">
+        <v>4</v>
+      </c>
       <c r="E578">
         <v>4</v>
       </c>
@@ -17188,6 +18010,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D579">
+        <v>1</v>
+      </c>
       <c r="E579">
         <v>1</v>
       </c>
@@ -17217,6 +18042,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D580">
+        <v>4</v>
+      </c>
       <c r="E580">
         <v>4</v>
       </c>
@@ -17246,6 +18074,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D581">
+        <v>4</v>
+      </c>
       <c r="E581">
         <v>4</v>
       </c>
@@ -17275,6 +18106,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D582">
+        <v>4</v>
+      </c>
       <c r="E582">
         <v>2</v>
       </c>
@@ -17304,6 +18138,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D583">
+        <v>4</v>
+      </c>
       <c r="E583">
         <v>4</v>
       </c>
@@ -17333,6 +18170,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D584">
+        <v>1</v>
+      </c>
       <c r="E584">
         <v>1</v>
       </c>
@@ -17362,6 +18202,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D585">
+        <v>4</v>
+      </c>
       <c r="E585">
         <v>4</v>
       </c>
@@ -17391,6 +18234,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D586">
+        <v>4</v>
+      </c>
       <c r="E586">
         <v>4</v>
       </c>
@@ -17420,6 +18266,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D587">
+        <v>1</v>
+      </c>
       <c r="E587">
         <v>1</v>
       </c>
@@ -17449,6 +18298,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D588">
+        <v>1</v>
+      </c>
       <c r="E588">
         <v>1</v>
       </c>
@@ -17478,6 +18330,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D589">
+        <v>1</v>
+      </c>
       <c r="E589">
         <v>1</v>
       </c>
@@ -17507,6 +18362,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D590">
+        <v>1</v>
+      </c>
       <c r="E590">
         <v>1</v>
       </c>
@@ -17536,6 +18394,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D591">
+        <v>1</v>
+      </c>
       <c r="E591">
         <v>1</v>
       </c>
@@ -17565,6 +18426,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D592">
+        <v>1</v>
+      </c>
       <c r="E592">
         <v>1</v>
       </c>
@@ -17594,6 +18458,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D593">
+        <v>1</v>
+      </c>
       <c r="E593">
         <v>1</v>
       </c>
@@ -17623,6 +18490,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D594">
+        <v>1</v>
+      </c>
       <c r="E594">
         <v>1</v>
       </c>
@@ -17652,6 +18522,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D595">
+        <v>1</v>
+      </c>
       <c r="E595">
         <v>1</v>
       </c>
@@ -17681,6 +18554,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D596">
+        <v>1</v>
+      </c>
       <c r="E596">
         <v>1</v>
       </c>
@@ -17710,6 +18586,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
       <c r="E597">
         <v>1</v>
       </c>
@@ -17739,6 +18618,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D598">
+        <v>1</v>
+      </c>
       <c r="E598">
         <v>1</v>
       </c>
@@ -17797,6 +18679,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D600">
+        <v>1</v>
+      </c>
       <c r="E600">
         <v>1</v>
       </c>
@@ -17826,6 +18711,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D601">
+        <v>1</v>
+      </c>
       <c r="E601">
         <v>1</v>
       </c>
@@ -17855,6 +18743,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D602">
+        <v>4</v>
+      </c>
       <c r="E602">
         <v>2</v>
       </c>
@@ -17884,6 +18775,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D603">
+        <v>4</v>
+      </c>
       <c r="E603">
         <v>2</v>
       </c>
@@ -17913,6 +18807,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D604">
+        <v>4</v>
+      </c>
       <c r="E604">
         <v>2</v>
       </c>
@@ -17942,6 +18839,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D605">
+        <v>4</v>
+      </c>
       <c r="E605">
         <v>2</v>
       </c>
@@ -17971,6 +18871,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D606">
+        <v>4</v>
+      </c>
       <c r="E606">
         <v>2</v>
       </c>
@@ -18000,6 +18903,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D607">
+        <v>4</v>
+      </c>
       <c r="E607">
         <v>2</v>
       </c>
@@ -18029,6 +18935,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D608">
+        <v>4</v>
+      </c>
       <c r="E608">
         <v>2</v>
       </c>
@@ -18058,6 +18967,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D609">
+        <v>4</v>
+      </c>
       <c r="E609">
         <v>2</v>
       </c>
@@ -18087,6 +18999,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D610">
+        <v>4</v>
+      </c>
       <c r="E610">
         <v>2</v>
       </c>
@@ -18116,6 +19031,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D611">
+        <v>4</v>
+      </c>
       <c r="E611">
         <v>1</v>
       </c>
@@ -18145,6 +19063,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D612">
+        <v>4</v>
+      </c>
       <c r="E612">
         <v>2</v>
       </c>
@@ -18174,6 +19095,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D613">
+        <v>4</v>
+      </c>
       <c r="E613">
         <v>2</v>
       </c>
@@ -18203,6 +19127,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D614">
+        <v>4</v>
+      </c>
       <c r="E614">
         <v>2</v>
       </c>
@@ -18216,17 +19143,857 @@
         <v>5</v>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Alkalinity (as calcium carbonate)</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D615">
+        <v>1</v>
+      </c>
+      <c r="E615">
+        <v>1</v>
+      </c>
+      <c r="F615">
+        <v>221</v>
+      </c>
+      <c r="G615">
+        <v>221</v>
+      </c>
+      <c r="H615">
+        <v>221</v>
+      </c>
+    </row>
     <row r="616">
-      <c r="A616" s="3" t="inlineStr">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Ammonia (as N)</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D616">
+        <v>1</v>
+      </c>
+      <c r="E616">
+        <v>1</v>
+      </c>
+      <c r="F616">
+        <v>6.52</v>
+      </c>
+      <c r="G616">
+        <v>6.52</v>
+      </c>
+      <c r="H616">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Arsenic</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D617">
+        <v>1</v>
+      </c>
+      <c r="E617">
+        <v>1</v>
+      </c>
+      <c r="F617" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G617" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H617" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Barium</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D618">
+        <v>1</v>
+      </c>
+      <c r="E618">
+        <v>1</v>
+      </c>
+      <c r="F618">
+        <v>0.421</v>
+      </c>
+      <c r="G618">
+        <v>0.421</v>
+      </c>
+      <c r="H618">
+        <v>0.421</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Cadmium</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D619">
+        <v>1</v>
+      </c>
+      <c r="E619">
+        <v>1</v>
+      </c>
+      <c r="F619" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="G619" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="H619" s="3">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Calcium</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D620">
+        <v>1</v>
+      </c>
+      <c r="E620">
+        <v>1</v>
+      </c>
+      <c r="F620">
+        <v>59</v>
+      </c>
+      <c r="G620">
+        <v>59</v>
+      </c>
+      <c r="H620">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Chloride</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D621">
+        <v>1</v>
+      </c>
+      <c r="E621">
+        <v>1</v>
+      </c>
+      <c r="F621">
+        <v>26</v>
+      </c>
+      <c r="G621">
+        <v>26</v>
+      </c>
+      <c r="H621">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Chromium (total)</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D622">
+        <v>1</v>
+      </c>
+      <c r="E622">
+        <v>1</v>
+      </c>
+      <c r="F622" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G622" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H622" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D623">
+        <v>1</v>
+      </c>
+      <c r="E623">
+        <v>1</v>
+      </c>
+      <c r="F623" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G623" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H623" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Conductivity</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>microsiemens per centimetre</t>
+        </is>
+      </c>
+      <c r="E624">
+        <v>1</v>
+      </c>
+      <c r="F624">
+        <v>524</v>
+      </c>
+      <c r="G624">
+        <v>560.5</v>
+      </c>
+      <c r="H624">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D625">
+        <v>1</v>
+      </c>
+      <c r="E625">
+        <v>1</v>
+      </c>
+      <c r="F625" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G625" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H625" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Fluoride</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D626">
+        <v>1</v>
+      </c>
+      <c r="E626">
+        <v>1</v>
+      </c>
+      <c r="F626" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G626" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="H626" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D627">
+        <v>1</v>
+      </c>
+      <c r="E627">
+        <v>1</v>
+      </c>
+      <c r="F627" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G627" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H627" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Magnesium</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D628">
+        <v>1</v>
+      </c>
+      <c r="E628">
+        <v>1</v>
+      </c>
+      <c r="F628">
+        <v>7</v>
+      </c>
+      <c r="G628">
+        <v>7</v>
+      </c>
+      <c r="H628">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D629">
+        <v>1</v>
+      </c>
+      <c r="E629">
+        <v>1</v>
+      </c>
+      <c r="F629">
+        <v>0.601</v>
+      </c>
+      <c r="G629">
+        <v>0.601</v>
+      </c>
+      <c r="H629">
+        <v>0.601</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D630">
+        <v>1</v>
+      </c>
+      <c r="E630">
+        <v>1</v>
+      </c>
+      <c r="F630" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="G630" s="3">
+        <v>0.0001</v>
+      </c>
+      <c r="H630" s="3">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Nickel</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D631">
+        <v>1</v>
+      </c>
+      <c r="E631">
+        <v>1</v>
+      </c>
+      <c r="F631" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="G631" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="H631" s="3">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Nitrate (as N)</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D632">
+        <v>1</v>
+      </c>
+      <c r="E632">
+        <v>1</v>
+      </c>
+      <c r="F632">
+        <v>0.01</v>
+      </c>
+      <c r="G632">
+        <v>0.01</v>
+      </c>
+      <c r="H632">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Nitrite (as N)</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D633">
+        <v>1</v>
+      </c>
+      <c r="E633">
+        <v>1</v>
+      </c>
+      <c r="F633" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G633" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="H633" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>pH units</t>
+        </is>
+      </c>
+      <c r="E634">
+        <v>1</v>
+      </c>
+      <c r="F634">
+        <v>6.6</v>
+      </c>
+      <c r="G634">
+        <v>6.82</v>
+      </c>
+      <c r="H634">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Potassium</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D635">
+        <v>1</v>
+      </c>
+      <c r="E635">
+        <v>1</v>
+      </c>
+      <c r="F635">
+        <v>21</v>
+      </c>
+      <c r="G635">
+        <v>21</v>
+      </c>
+      <c r="H635">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Sodium</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D636">
+        <v>1</v>
+      </c>
+      <c r="E636">
+        <v>1</v>
+      </c>
+      <c r="F636">
+        <v>24</v>
+      </c>
+      <c r="G636">
+        <v>24</v>
+      </c>
+      <c r="H636">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Sulfate</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D637">
+        <v>1</v>
+      </c>
+      <c r="E637">
+        <v>1</v>
+      </c>
+      <c r="F637">
+        <v>1</v>
+      </c>
+      <c r="G637">
+        <v>1</v>
+      </c>
+      <c r="H637">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Total Dissolved Solids</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D638">
+        <v>1</v>
+      </c>
+      <c r="E638">
+        <v>1</v>
+      </c>
+      <c r="F638">
+        <v>341</v>
+      </c>
+      <c r="G638">
+        <v>341</v>
+      </c>
+      <c r="H638">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Total Organic Carbon</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D639">
+        <v>1</v>
+      </c>
+      <c r="E639">
+        <v>1</v>
+      </c>
+      <c r="F639">
+        <v>6</v>
+      </c>
+      <c r="G639">
+        <v>6</v>
+      </c>
+      <c r="H639">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>milligrams per litre</t>
+        </is>
+      </c>
+      <c r="D640">
+        <v>1</v>
+      </c>
+      <c r="E640">
+        <v>1</v>
+      </c>
+      <c r="F640" s="3">
+        <v>0.005</v>
+      </c>
+      <c r="G640" s="3">
+        <v>0.005</v>
+      </c>
+      <c r="H640" s="3">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="3" t="inlineStr">
         <is>
           <t>Note on values below the analytical detection limit. Where a result was below the detection limit for the analysis, the figure shown is that detection limit rather than a measured concentration, in accordance with the convention stated in the licence Dictionary. The exception is Methane, which the field instrument records as zero when none is detected. Such figures are shown in grey italics.</t>
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" s="3" t="inlineStr">
+    <row r="643">
+      <c r="A643" s="3" t="inlineStr">
         <is>
           <t>A Lowest or Highest value in grey italics was attained only by below-detection results. A Mean in grey italics indicates that every result for that monitoring point and pollutant was below detection. Figures in normal type are measured values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="3" t="inlineStr">
+        <is>
+          <t>No. of samples required is taken from licence conditions M2.2 and M2.3 (Quarterly = 4, Yearly = 1). It is left blank where the licence sets no requirement for that pollutant at that point, and for points 2 and 3, where condition M2.4(a) Special Frequency 1 requires sampling within the first 24 hours of each discharge rather than a fixed number of samples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="3" t="inlineStr">
+        <is>
+          <t>At point 1 the number of samples collected counts individual grid locations. The quarterly requirement refers to monitoring events.</t>
         </is>
       </c>
     </row>
